--- a/git 学習資料.xlsx
+++ b/git 学習資料.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/20fcbadadf1d6d91/ドキュメント/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C23A3765-C448-47E2-B10B-C44B1F3ACB33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{C23A3765-C448-47E2-B10B-C44B1F3ACB33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{231BA186-2D98-42AE-9D3F-7A51BE4742E9}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{583628DA-0B58-400F-8400-1EF8F6B2194F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{583628DA-0B58-400F-8400-1EF8F6B2194F}"/>
   </bookViews>
   <sheets>
     <sheet name="git基本概要" sheetId="1" r:id="rId1"/>
     <sheet name="git用語関係" sheetId="2" r:id="rId2"/>
+    <sheet name="基本操作" sheetId="3" r:id="rId3"/>
+    <sheet name="マージについて" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,13 +37,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="71">
   <si>
     <t>gitについての学習</t>
     <rPh sb="8" eb="10">
       <t>ガクシュウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>分散型バージョン管理システム。Gitによってファイルの</t>
@@ -51,7 +53,7 @@
     <rPh sb="8" eb="10">
       <t>カンリ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>バージョンを管理することができるため、他の誰かにソース</t>
@@ -64,7 +66,7 @@
     <rPh sb="21" eb="22">
       <t>ダレ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>コードが上書きされても簡単にもとに戻せる</t>
@@ -77,7 +79,7 @@
     <rPh sb="17" eb="18">
       <t>モド</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Gitとはソースや変更履歴を管理するために行われる、</t>
@@ -90,7 +92,7 @@
     <rPh sb="21" eb="22">
       <t>オコナ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>修正版や更新版などのファイルが増えてどのファイルを編集すれば</t>
@@ -106,7 +108,7 @@
     <rPh sb="25" eb="27">
       <t>ヘンシュウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>良いかが分からない。</t>
@@ -116,11 +118,11 @@
     <rPh sb="4" eb="5">
       <t>ワ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>　　gitがあれば、、、</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>いつ・誰が・どのように変更したかといった変更履歴とともにファイルを</t>
@@ -133,7 +135,7 @@
     <rPh sb="20" eb="24">
       <t>ヘンコウリレキ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>保存できるため、もし誤って上書きしたとしても任意のバージョンへ簡単に</t>
@@ -152,14 +154,14 @@
     <rPh sb="31" eb="33">
       <t>カンタン</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>戻すことができる。</t>
     <rPh sb="0" eb="1">
       <t>モド</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Gitを使うことで古いバージョンから新しいバージョンのファイルまで1元的に</t>
@@ -178,7 +180,7 @@
     <rPh sb="35" eb="36">
       <t>テキ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>管理が可能になる。修正をする際に新しいファイルを増やしたり見分けがつくように</t>
@@ -203,7 +205,7 @@
     <rPh sb="29" eb="31">
       <t>ミワ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ファイル名を変える必要がなくなるため、ファイル管理がしやすい。</t>
@@ -219,7 +221,7 @@
     <rPh sb="23" eb="25">
       <t>カンリ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Gitはネットワークを経由して複数人でファイルや変更履歴を共有する機能もある。</t>
@@ -238,7 +240,7 @@
     <rPh sb="33" eb="35">
       <t>キノウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>共有ストレージ上のファイルを共同で編集する場合、バージョンごとなどでファイル</t>
@@ -257,7 +259,7 @@
     <rPh sb="21" eb="23">
       <t>バアイ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>が作成されフォルダが煩雑になっていたが、Gitを使うことで、ファイルが増えなくなった</t>
@@ -270,7 +272,7 @@
     <rPh sb="35" eb="36">
       <t>フ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>・リモートにあるファイルや変更履歴を自分のパソコンに取り込む(コピーする)</t>
@@ -286,7 +288,7 @@
     <rPh sb="28" eb="29">
       <t>コ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>・他の人の行った修正を手元のファイルに反映させる</t>
@@ -308,7 +310,7 @@
     <rPh sb="19" eb="21">
       <t>ハンエイ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>・バグ修正用の機能追加用などで、変更履歴を自由に枝分かれさせたり（ブランチを</t>
@@ -330,7 +332,7 @@
     <rPh sb="24" eb="26">
       <t>エダワ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>切ったり)、その枝分かれを統合したり(マージしたり)出来る、など</t>
@@ -346,7 +348,7 @@
     <rPh sb="26" eb="28">
       <t>デキ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>2.Gitを使うメリット、Gitで出来る事</t>
@@ -359,7 +361,7 @@
     <rPh sb="20" eb="21">
       <t>コト</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>1 古いバージョンから新しいバージョンのファイルまで管理することができる</t>
@@ -372,7 +374,7 @@
     <rPh sb="26" eb="28">
       <t>カンリ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>2 チームでファイルや変更履歴をスムーズに共有できる</t>
@@ -382,7 +384,7 @@
     <rPh sb="21" eb="23">
       <t>キョウユウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>3　豊富な機能を使いチームで共同開発を効率化できる</t>
@@ -404,7 +406,7 @@
     <rPh sb="21" eb="22">
       <t>カ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>複数の作業者が共同で編集しているとき、よくあるのが</t>
@@ -420,33 +422,412 @@
     <rPh sb="10" eb="12">
       <t>ヘンシュウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>1.背景</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>リポジトリ・コミット・プル・プッシュ</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コミット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>用語名</t>
+    <rPh sb="0" eb="3">
+      <t>ヨウゴメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>概要</t>
+    <rPh sb="0" eb="2">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リポジトリ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プッシュ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クローン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ファイルや変更履歴を保存しておくデータベース
+ローカルにある「ローカルリポジトリ」とネットワーク上にある
+「リモートリポジトリ」がある。</t>
+    <rPh sb="5" eb="9">
+      <t>ヘンコウリレキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ホゾン</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>ジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ファイルや変更履歴をリポジトリへ登録すること</t>
+    <rPh sb="5" eb="9">
+      <t>ヘンコウリレキ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リモートリポジトリのコミットを、ローカルリポジトリへ反映させる
+プルを行うことで、リモートリポジトリ上のファイルや変更履歴が、
+ローカルリポジトリへダウンロードされる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リモートリポジトリのコミットを、ローカルリポジトリへコピーする
+プルとの違いは、プルでは差分のみコピーするのに対し、クローンでは丸ごとコピーする点にある。
+そのため何も登録されていないローカルリポジトリへコピーしたいときは、クローンを使う。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コミットをローカルリポジトリからリモートリポジトリへ反映させる
+プッシュを行うことで、ローカルリポジトリ上のファイルや変更履歴
+がローカルリポジトリへダウンロードされる</t>
+    <rPh sb="26" eb="28">
+      <t>ハンエイ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="59" eb="63">
+      <t>ヘンコウリレキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１．新しいリポジトリを作成する。</t>
+    <rPh sb="2" eb="3">
+      <t>アタラ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ディレクトリの作成</t>
+    <rPh sb="7" eb="9">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>git init</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>←Gitの管理下にする</t>
+    <rPh sb="5" eb="8">
+      <t>カンリカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>２．ファイルをコミットする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワークツリーとインデックスの状態を確認する</t>
+    <rPh sb="14" eb="16">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>git status</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3.ファイルをインデックスに登録する</t>
+    <rPh sb="14" eb="16">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>← fileはインデックスに登録するファイルを指定する。</t>
+    <rPh sb="14" eb="16">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>←すべてのファイルをインデックスに登録することができる。</t>
+    <rPh sb="17" eb="19">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4.コミットする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>git commit -m "コメント"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="5"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">git add . </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>git add &lt;file&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5.リモートリポジトリにプッシュする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リモートリポジトリで自分の手元のローカルリポジトリの変更履歴を共有するには</t>
+    <rPh sb="10" eb="12">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>テモト</t>
+    </rPh>
+    <rPh sb="26" eb="30">
+      <t>ヘンコウリレキ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>キョウユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ローカルリポジトリ内の変更履歴をアップロードする。</t>
+    <rPh sb="9" eb="10">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ヘンコウリレキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ローカルリポジトリ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>git push -u origin main</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変更履歴のマージ</t>
+    <rPh sb="0" eb="4">
+      <t>ヘンコウリレキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・・・指定したブランチの内容を取り込む</t>
+    <rPh sb="3" eb="5">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>合体</t>
+    <rPh sb="0" eb="2">
+      <t>ガッタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>顧客</t>
+    <rPh sb="0" eb="2">
+      <t>コキャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>売上</t>
+    <rPh sb="0" eb="2">
+      <t>ウリアゲ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>注意点</t>
+    <rPh sb="0" eb="3">
+      <t>チュウイテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最後にpullを実行してから次のpushをするまでの間に、他の</t>
+    <rPh sb="0" eb="2">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ホカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人がpushをしてリモートリポジトリを更新してしまった場合</t>
+    <rPh sb="0" eb="1">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>には自分のpushが拒否されてしまう(コンフリクト)</t>
+    <rPh sb="2" eb="4">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キョヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンフリクトを起こさないために一度マージを行い他の履歴</t>
+    <rPh sb="7" eb="8">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ホカ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>リレキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>での変更を取り込み、そのあとにマージを行う</t>
+    <rPh sb="2" eb="4">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -460,14 +841,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="13"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
@@ -475,16 +848,91 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFA20000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFA20000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="5"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCECFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -572,13 +1020,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -594,9 +1094,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -609,10 +1106,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -621,12 +1115,62 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCCECFF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -707,16 +1251,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>28574</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>53974</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>203199</xdr:rowOff>
+      <xdr:rowOff>95249</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>6349</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>31749</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>155574</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -731,12 +1275,12 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2657474" y="888999"/>
-          <a:ext cx="1292225" cy="866775"/>
+          <a:off x="3419474" y="781049"/>
+          <a:ext cx="1298575" cy="838201"/>
         </a:xfrm>
         <a:prstGeom prst="can">
           <a:avLst>
-            <a:gd name="adj" fmla="val 37658"/>
+            <a:gd name="adj" fmla="val 21749"/>
           </a:avLst>
         </a:prstGeom>
       </xdr:spPr>
@@ -760,8 +1304,19 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>リモート</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>リポジトリ</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -769,16 +1324,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>19051</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>939801</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>206375</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2241551</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -793,14 +1348,377 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1333501" y="2082800"/>
-          <a:ext cx="1295400" cy="866775"/>
+          <a:off x="1600201" y="2057400"/>
+          <a:ext cx="1301750" cy="965200"/>
         </a:xfrm>
         <a:prstGeom prst="can">
           <a:avLst>
-            <a:gd name="adj" fmla="val 37658"/>
+            <a:gd name="adj" fmla="val 26669"/>
           </a:avLst>
         </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ローカル</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>リポジトリ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="円柱 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B09126B-5E65-4DEB-9334-73100DDF6F1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5346700" y="1974850"/>
+          <a:ext cx="1327150" cy="946150"/>
+        </a:xfrm>
+        <a:prstGeom prst="can">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 26669"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ローカル</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>リポジトリ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>31749</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>3175</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="直線矢印コネクタ 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BEACF2A-3819-2D61-28B1-BBEA267E50A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="1"/>
+          <a:endCxn id="2" idx="4"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="4718049" y="1200150"/>
+          <a:ext cx="1292226" cy="774700"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1590676</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>53974</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B1ACE57-3FB0-840C-07CD-5A1D1403B035}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="2"/>
+          <a:endCxn id="3" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2251076" y="1200150"/>
+          <a:ext cx="1168398" cy="857250"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="グラフィックス 44" descr="ノート PC 単色塗りつぶし">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFEEAEE9-060A-936C-A884-D4F0542CA05F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6985000" y="3079750"/>
+          <a:ext cx="1111250" cy="1111250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1162050</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="グラフィックス 45" descr="ノート PC 単色塗りつぶし">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AF118AC-1E60-421C-A65A-0A9CFE64D3E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="711200" y="3073400"/>
+          <a:ext cx="1111250" cy="1111250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="矢印: 上向き折線 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0C42726-D570-5FB8-9EF5-29AA089D5E19}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="5880100" y="3016250"/>
+          <a:ext cx="952500" cy="469900"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentUpArrow">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 13895"/>
+            <a:gd name="adj2" fmla="val 25000"/>
+            <a:gd name="adj3" fmla="val 27899"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -832,22 +1750,323 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:colOff>654050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>654050</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>206375</xdr:rowOff>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="円柱 3">
+        <xdr:cNvPr id="50" name="テキスト ボックス 49">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B09126B-5E65-4DEB-9334-73100DDF6F1A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24DE6AB8-02CF-B57C-9639-8A6725728E38}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6000750" y="3549650"/>
+          <a:ext cx="806450" cy="596900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>コミット</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>（登録）</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>536709</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>190040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>479559</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>193496</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="テキスト ボックス 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAB7AA10-5535-4695-BFE2-9F6CD82972A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="2807547">
+          <a:off x="4837106" y="1033143"/>
+          <a:ext cx="1375056" cy="603250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:scene3d>
+          <a:camera prst="orthographicFront">
+            <a:rot lat="0" lon="0" rev="900000"/>
+          </a:camera>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>プッシュ</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>（アップロード）</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1721203</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>42593</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2304877</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>39470</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="テキスト ボックス 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36D9C46E-4544-426D-82CA-6C1F34572751}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="18769824">
+          <a:off x="1989201" y="1120795"/>
+          <a:ext cx="1368477" cy="583674"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+        <a:scene3d>
+          <a:camera prst="orthographicFront">
+            <a:rot lat="0" lon="0" rev="21000000"/>
+          </a:camera>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>プル</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>（ダウンロード）</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>215900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="テキスト ボックス 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E40A5FB8-D9F0-4B85-A466-5D72A143E0D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="2959100"/>
+          <a:ext cx="3689350" cy="273050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>（データベース）</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC759253-67F4-44DE-9EC0-52037D25A90A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -855,13 +2074,498 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3933825" y="2082800"/>
-          <a:ext cx="1320800" cy="866775"/>
+          <a:off x="1524000" y="4772025"/>
+          <a:ext cx="885825" cy="600075"/>
         </a:xfrm>
-        <a:prstGeom prst="can">
-          <a:avLst>
-            <a:gd name="adj" fmla="val 37658"/>
-          </a:avLst>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>html</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>206375</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE26E3EE-0FE4-4BE9-BA8D-8D8377F36992}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1533525" y="5524500"/>
+          <a:ext cx="885825" cy="596900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>css</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C055552-CAC7-4ADE-B453-2D4F6444774A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4162425" y="4752975"/>
+          <a:ext cx="885825" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>html</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A740DAB6-B59F-4725-B64F-DF94AFB0F840}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4171950" y="5514975"/>
+          <a:ext cx="885825" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>css</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>15875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="直線矢印コネクタ 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D78AB52-FFEC-6E12-248C-3165F6249220}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2695575" y="5473700"/>
+          <a:ext cx="1111250" cy="3175"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="テキスト ボックス 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EEC1A0B6-853D-531B-CDE5-F906A36E3F4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2705100" y="5591175"/>
+          <a:ext cx="1123950" cy="314325"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>Push</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49424512-7423-2CE1-9FDA-E40451CCCE27}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="762000" y="533399"/>
+          <a:ext cx="3305175" cy="2505075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>206375</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>463550</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="矢印: 下 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5927F0BF-F6B3-E2BF-CA45-38705628D2E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1520825" y="1362075"/>
+          <a:ext cx="257175" cy="485775"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
       <xdr:style>
@@ -889,6 +2593,94 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>587375</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>606425</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>107432</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F43BC7EF-AFA6-CE89-B4D7-36E600F09E0B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="587375" y="4216400"/>
+          <a:ext cx="3962400" cy="1891782"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>454025</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>44564</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1557504-EE53-A80C-696A-0F286A3E1625}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="454025" y="6800851"/>
+          <a:ext cx="4191114" cy="1733550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1213,60 +3005,48 @@
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6"/>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="6"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6"/>
+      <c r="G5" s="5"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="4"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="2"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="10" t="s">
+      <c r="B8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="10" t="s">
+      <c r="B9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="10" t="s">
+      <c r="B10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="10" t="s">
+      <c r="B11" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1291,12 +3071,12 @@
       </c>
     </row>
     <row r="17" spans="2:2" ht="21.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1316,7 +3096,7 @@
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="11" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1336,7 +3116,7 @@
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="11" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1361,7 +3141,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1369,8 +3149,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1747EEB-108F-466B-B83C-5B54729096C5}">
-  <dimension ref="B2:J19"/>
+  <dimension ref="B2:J26"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="35.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" t="s">
@@ -1390,181 +3173,461 @@
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="6"/>
+      <c r="J4" s="5"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="6"/>
+      <c r="J5" s="5"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="6"/>
+      <c r="J6" s="5"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="6"/>
+      <c r="J7" s="5"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="6"/>
+      <c r="J8" s="5"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="6"/>
+      <c r="J9" s="5"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="6"/>
+      <c r="J10" s="5"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="6"/>
+      <c r="J11" s="5"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="6"/>
+      <c r="J12" s="5"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="4"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="6"/>
+      <c r="J13" s="5"/>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="4"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="6"/>
+      <c r="J14" s="5"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="4"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="6"/>
+      <c r="J15" s="5"/>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="4"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="6"/>
+      <c r="J16" s="5"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="4"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="6"/>
+      <c r="J17" s="5"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="4"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="6"/>
+      <c r="J18" s="5"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="7"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="9"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="8"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+    </row>
+    <row r="22" spans="2:10" ht="72" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+    </row>
+    <row r="24" spans="2:10" ht="58" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+    </row>
+    <row r="25" spans="2:10" ht="71" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+    </row>
+    <row r="26" spans="2:10" ht="94" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <mergeCells count="6">
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C25:I25"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE1533A8-404A-46E8-B9D3-BFCAC94D67A9}">
+  <dimension ref="B1:I29"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="2:4" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="21" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="1"/>
+      <c r="C19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="4"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27" s="4"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="5"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="8"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C8D444-1143-4045-920D-F68F4A023957}">
+  <dimension ref="B1:E29"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="2:5" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C4" s="24"/>
+      <c r="E4" s="24"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C5" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C6" s="25"/>
+      <c r="E6" s="25"/>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="E8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D9" s="24"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D10" s="26" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D11" s="26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D12" s="25"/>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" t="s">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
